--- a/BWI/bestwine_output/bestwine_China.xlsx
+++ b/BWI/bestwine_output/bestwine_China.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA172"/>
+  <dimension ref="A1:AA176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -17683,6 +17683,394 @@
       <c r="Z172" s="2" t="inlineStr"/>
       <c r="AA172" s="2" t="inlineStr"/>
     </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>Rainbow Digital Commerce Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>Rainbow Digital Commerce Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>89356</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>Shenzhen Shi</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>Guangdong Sheng</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>Zhong Xin Lu</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>518067</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="inlineStr">
+        <is>
+          <t>http://www.tianhong.cn</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="inlineStr"/>
+      <c r="K173" s="2" t="inlineStr"/>
+      <c r="L173" s="2" t="inlineStr">
+        <is>
+          <t>1380</t>
+        </is>
+      </c>
+      <c r="M173" s="2" t="inlineStr"/>
+      <c r="N173" s="2" t="inlineStr">
+        <is>
+          <t>myrainbow@rainbowcn.com</t>
+        </is>
+      </c>
+      <c r="O173" s="2" t="inlineStr">
+        <is>
+          <t>+86 400 829 5295</t>
+        </is>
+      </c>
+      <c r="P173" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q173" s="2" t="inlineStr">
+        <is>
+          <t>913601007391666077</t>
+        </is>
+      </c>
+      <c r="R173" s="2" t="inlineStr"/>
+      <c r="S173" s="2" t="inlineStr"/>
+      <c r="T173" s="2" t="inlineStr"/>
+      <c r="U173" s="2" t="inlineStr"/>
+      <c r="V173" s="2" t="inlineStr"/>
+      <c r="W173" s="2" t="inlineStr"/>
+      <c r="X173" s="2" t="inlineStr"/>
+      <c r="Y173" s="2" t="inlineStr"/>
+      <c r="Z173" s="2" t="inlineStr"/>
+      <c r="AA173" s="2" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>Summergate International Trading (shanghai) Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>Summergate International Trading (shanghai) Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>2872</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kou Qu</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>Shang Hai Shi</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>328 Tian Tong Lu, Luxun Park</t>
+        </is>
+      </c>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>200080</t>
+        </is>
+      </c>
+      <c r="I174" s="2" t="inlineStr">
+        <is>
+          <t>https://summergate.com</t>
+        </is>
+      </c>
+      <c r="J174" s="2" t="inlineStr"/>
+      <c r="K174" s="2" t="inlineStr"/>
+      <c r="L174" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="M174" s="2" t="inlineStr"/>
+      <c r="N174" s="2" t="inlineStr">
+        <is>
+          <t>info@summergate.com</t>
+        </is>
+      </c>
+      <c r="O174" s="2" t="inlineStr">
+        <is>
+          <t>+86 21 6329 4433</t>
+        </is>
+      </c>
+      <c r="P174" s="2" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="Q174" s="2" t="inlineStr">
+        <is>
+          <t>91310000703003881C</t>
+        </is>
+      </c>
+      <c r="R174" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/summergate/</t>
+        </is>
+      </c>
+      <c r="S174" s="2" t="inlineStr"/>
+      <c r="T174" s="2" t="inlineStr"/>
+      <c r="U174" s="2" t="inlineStr"/>
+      <c r="V174" s="2" t="inlineStr"/>
+      <c r="W174" s="2" t="inlineStr">
+        <is>
+          <t>Dan Christensen</t>
+        </is>
+      </c>
+      <c r="X174" s="2" t="inlineStr">
+        <is>
+          <t>Sales Supervisor</t>
+        </is>
+      </c>
+      <c r="Y174" s="2" t="inlineStr"/>
+      <c r="Z174" s="2" t="inlineStr"/>
+      <c r="AA174" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/dan-christensen-9307a110/</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>Summergate International Trading (shanghai) Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>Summergate International Trading (shanghai) Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>2872</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kou Qu</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>Shang Hai Shi</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>328 Tian Tong Lu, Luxun Park</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>200080</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="inlineStr">
+        <is>
+          <t>https://summergate.com</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="inlineStr"/>
+      <c r="K175" s="2" t="inlineStr"/>
+      <c r="L175" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="M175" s="2" t="inlineStr"/>
+      <c r="N175" s="2" t="inlineStr">
+        <is>
+          <t>info@summergate.com</t>
+        </is>
+      </c>
+      <c r="O175" s="2" t="inlineStr">
+        <is>
+          <t>+86 21 6329 4433</t>
+        </is>
+      </c>
+      <c r="P175" s="2" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="Q175" s="2" t="inlineStr">
+        <is>
+          <t>91310000703003881C</t>
+        </is>
+      </c>
+      <c r="R175" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/summergate/</t>
+        </is>
+      </c>
+      <c r="S175" s="2" t="inlineStr"/>
+      <c r="T175" s="2" t="inlineStr"/>
+      <c r="U175" s="2" t="inlineStr"/>
+      <c r="V175" s="2" t="inlineStr"/>
+      <c r="W175" s="2" t="inlineStr">
+        <is>
+          <t>Levon Gao</t>
+        </is>
+      </c>
+      <c r="X175" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y175" s="2" t="inlineStr"/>
+      <c r="Z175" s="2" t="inlineStr"/>
+      <c r="AA175" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/levon-gao-65a16997/</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>Summergate International Trading (shanghai) Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>Summergate International Trading (shanghai) Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>2872</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kou Qu</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>Shang Hai Shi</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>328 Tian Tong Lu, Luxun Park</t>
+        </is>
+      </c>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>200080</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="inlineStr">
+        <is>
+          <t>https://summergate.com</t>
+        </is>
+      </c>
+      <c r="J176" s="2" t="inlineStr"/>
+      <c r="K176" s="2" t="inlineStr"/>
+      <c r="L176" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="M176" s="2" t="inlineStr"/>
+      <c r="N176" s="2" t="inlineStr">
+        <is>
+          <t>info@summergate.com</t>
+        </is>
+      </c>
+      <c r="O176" s="2" t="inlineStr">
+        <is>
+          <t>+86 21 6329 4433</t>
+        </is>
+      </c>
+      <c r="P176" s="2" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="Q176" s="2" t="inlineStr">
+        <is>
+          <t>91310000703003881C</t>
+        </is>
+      </c>
+      <c r="R176" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/summergate/</t>
+        </is>
+      </c>
+      <c r="S176" s="2" t="inlineStr"/>
+      <c r="T176" s="2" t="inlineStr"/>
+      <c r="U176" s="2" t="inlineStr"/>
+      <c r="V176" s="2" t="inlineStr"/>
+      <c r="W176" s="2" t="inlineStr">
+        <is>
+          <t>Delphine Hu</t>
+        </is>
+      </c>
+      <c r="X176" s="2" t="inlineStr">
+        <is>
+          <t>Wine Purchasing Manager</t>
+        </is>
+      </c>
+      <c r="Y176" s="2" t="inlineStr"/>
+      <c r="Z176" s="2" t="inlineStr"/>
+      <c r="AA176" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/in/%e4%bd%b3%e8%8f%b2-%e8%83%a1-8ab21592/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_China.xlsx
+++ b/BWI/bestwine_output/bestwine_China.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA176"/>
+  <dimension ref="A1:AA177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -18071,6 +18071,79 @@
         </is>
       </c>
     </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>Xiamen Zunzhi Trading Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>Xiamen Zunzhi Wine</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>30123</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>Xiamen</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>Fujian</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>101-102, 915 Huancheng West Road, Tong'an District</t>
+        </is>
+      </c>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t>250100</t>
+        </is>
+      </c>
+      <c r="I177" s="2" t="inlineStr">
+        <is>
+          <t>http://www.zunzhiwine.cn</t>
+        </is>
+      </c>
+      <c r="J177" s="2" t="inlineStr"/>
+      <c r="K177" s="2" t="inlineStr"/>
+      <c r="L177" s="2" t="inlineStr"/>
+      <c r="M177" s="2" t="inlineStr"/>
+      <c r="N177" s="2" t="inlineStr">
+        <is>
+          <t>cherry@powerlinkco.com</t>
+        </is>
+      </c>
+      <c r="O177" s="2" t="inlineStr">
+        <is>
+          <t>+86 592 789 3351</t>
+        </is>
+      </c>
+      <c r="P177" s="2" t="inlineStr"/>
+      <c r="Q177" s="2" t="inlineStr"/>
+      <c r="R177" s="2" t="inlineStr"/>
+      <c r="S177" s="2" t="inlineStr"/>
+      <c r="T177" s="2" t="inlineStr"/>
+      <c r="U177" s="2" t="inlineStr"/>
+      <c r="V177" s="2" t="inlineStr"/>
+      <c r="W177" s="2" t="inlineStr"/>
+      <c r="X177" s="2" t="inlineStr"/>
+      <c r="Y177" s="2" t="inlineStr"/>
+      <c r="Z177" s="2" t="inlineStr"/>
+      <c r="AA177" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_China.xlsx
+++ b/BWI/bestwine_output/bestwine_China.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA177"/>
+  <dimension ref="A1:AA179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -18144,6 +18144,232 @@
       <c r="Z177" s="2" t="inlineStr"/>
       <c r="AA177" s="2" t="inlineStr"/>
     </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>Cofco Corporation</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>Cofco Corporation</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>35571</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>Dongcheng</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>Cofco Fortune Plaza, No.8, Chao Yang Men South St., Chao Yang District</t>
+        </is>
+      </c>
+      <c r="H178" s="2" t="inlineStr">
+        <is>
+          <t>100020</t>
+        </is>
+      </c>
+      <c r="I178" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cofco.com, https://www.cofcointernational.com</t>
+        </is>
+      </c>
+      <c r="J178" s="2" t="inlineStr"/>
+      <c r="K178" s="2" t="inlineStr"/>
+      <c r="L178" s="2" t="inlineStr">
+        <is>
+          <t>1806</t>
+        </is>
+      </c>
+      <c r="M178" s="2" t="inlineStr"/>
+      <c r="N178" s="2" t="inlineStr">
+        <is>
+          <t>cofco-news@cofco.com</t>
+        </is>
+      </c>
+      <c r="O178" s="2" t="inlineStr">
+        <is>
+          <t>+86 10 8500 6688</t>
+        </is>
+      </c>
+      <c r="P178" s="2" t="inlineStr">
+        <is>
+          <t>1983</t>
+        </is>
+      </c>
+      <c r="Q178" s="2" t="inlineStr">
+        <is>
+          <t>91110000101100414N</t>
+        </is>
+      </c>
+      <c r="R178" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/cofco-corporation</t>
+        </is>
+      </c>
+      <c r="S178" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/COFCO1949/</t>
+        </is>
+      </c>
+      <c r="T178" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cofcointl/</t>
+        </is>
+      </c>
+      <c r="U178" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/COFCOINTL</t>
+        </is>
+      </c>
+      <c r="V178" s="2" t="inlineStr"/>
+      <c r="W178" s="2" t="inlineStr">
+        <is>
+          <t>Jack Yang</t>
+        </is>
+      </c>
+      <c r="X178" s="2" t="inlineStr">
+        <is>
+          <t>Import And Brand Manager</t>
+        </is>
+      </c>
+      <c r="Y178" s="2" t="inlineStr"/>
+      <c r="Z178" s="2" t="inlineStr"/>
+      <c r="AA178" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jack-yang-86178a53/</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>Cofco Corporation</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>Cofco Corporation</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>35571</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>Dongcheng</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>Cofco Fortune Plaza, No.8, Chao Yang Men South St., Chao Yang District</t>
+        </is>
+      </c>
+      <c r="H179" s="2" t="inlineStr">
+        <is>
+          <t>100020</t>
+        </is>
+      </c>
+      <c r="I179" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cofco.com, https://www.cofcointernational.com</t>
+        </is>
+      </c>
+      <c r="J179" s="2" t="inlineStr"/>
+      <c r="K179" s="2" t="inlineStr"/>
+      <c r="L179" s="2" t="inlineStr">
+        <is>
+          <t>1806</t>
+        </is>
+      </c>
+      <c r="M179" s="2" t="inlineStr"/>
+      <c r="N179" s="2" t="inlineStr">
+        <is>
+          <t>cofco-news@cofco.com</t>
+        </is>
+      </c>
+      <c r="O179" s="2" t="inlineStr">
+        <is>
+          <t>+86 10 8500 6688</t>
+        </is>
+      </c>
+      <c r="P179" s="2" t="inlineStr">
+        <is>
+          <t>1983</t>
+        </is>
+      </c>
+      <c r="Q179" s="2" t="inlineStr">
+        <is>
+          <t>91110000101100414N</t>
+        </is>
+      </c>
+      <c r="R179" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/cofco-corporation</t>
+        </is>
+      </c>
+      <c r="S179" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/COFCO1949/</t>
+        </is>
+      </c>
+      <c r="T179" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cofcointl/</t>
+        </is>
+      </c>
+      <c r="U179" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/COFCOINTL</t>
+        </is>
+      </c>
+      <c r="V179" s="2" t="inlineStr"/>
+      <c r="W179" s="2" t="inlineStr">
+        <is>
+          <t>Randy Zhou</t>
+        </is>
+      </c>
+      <c r="X179" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manger of Import Wine Division</t>
+        </is>
+      </c>
+      <c r="Y179" s="2" t="inlineStr"/>
+      <c r="Z179" s="2" t="inlineStr"/>
+      <c r="AA179" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/randy-zhou-04b80435/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_China.xlsx
+++ b/BWI/bestwine_output/bestwine_China.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA179"/>
+  <dimension ref="A1:AA207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -18370,6 +18370,1930 @@
         </is>
       </c>
     </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>Yotone Wine Huizhou</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr"/>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>168430</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>Huizhou City</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>Guangdong Province</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>No. 27, Renmin Fourth Road, Danshui Street, Huiyang District</t>
+        </is>
+      </c>
+      <c r="H180" s="2" t="inlineStr"/>
+      <c r="I180" s="2" t="inlineStr">
+        <is>
+          <t>https://yotonewines.com</t>
+        </is>
+      </c>
+      <c r="J180" s="2" t="inlineStr"/>
+      <c r="K180" s="2" t="inlineStr"/>
+      <c r="L180" s="2" t="inlineStr"/>
+      <c r="M180" s="2" t="inlineStr"/>
+      <c r="N180" s="2" t="inlineStr">
+        <is>
+          <t>service@yotonewines.com</t>
+        </is>
+      </c>
+      <c r="O180" s="2" t="inlineStr">
+        <is>
+          <t>+86 752 266 0336</t>
+        </is>
+      </c>
+      <c r="P180" s="2" t="inlineStr"/>
+      <c r="Q180" s="2" t="inlineStr"/>
+      <c r="R180" s="2" t="inlineStr"/>
+      <c r="S180" s="2" t="inlineStr"/>
+      <c r="T180" s="2" t="inlineStr"/>
+      <c r="U180" s="2" t="inlineStr"/>
+      <c r="V180" s="2" t="inlineStr"/>
+      <c r="W180" s="2" t="inlineStr">
+        <is>
+          <t>Olivier Sublett</t>
+        </is>
+      </c>
+      <c r="X180" s="2" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="Y180" s="2" t="inlineStr"/>
+      <c r="Z180" s="2" t="inlineStr"/>
+      <c r="AA180" s="2" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>Wenzhou Fattoria Wine</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr"/>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>168429</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>Wenzhou City</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>Zhejiang Province</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>No. 1067 Jinxiu Road, Lucheng District</t>
+        </is>
+      </c>
+      <c r="H181" s="2" t="inlineStr"/>
+      <c r="I181" s="2" t="inlineStr">
+        <is>
+          <t>https://fattoriawine.com</t>
+        </is>
+      </c>
+      <c r="J181" s="2" t="inlineStr"/>
+      <c r="K181" s="2" t="inlineStr"/>
+      <c r="L181" s="2" t="inlineStr"/>
+      <c r="M181" s="2" t="inlineStr"/>
+      <c r="N181" s="2" t="inlineStr">
+        <is>
+          <t>fdgd@qq.com</t>
+        </is>
+      </c>
+      <c r="O181" s="2" t="inlineStr">
+        <is>
+          <t>+86 577 8886 7719</t>
+        </is>
+      </c>
+      <c r="P181" s="2" t="inlineStr"/>
+      <c r="Q181" s="2" t="inlineStr"/>
+      <c r="R181" s="2" t="inlineStr"/>
+      <c r="S181" s="2" t="inlineStr"/>
+      <c r="T181" s="2" t="inlineStr"/>
+      <c r="U181" s="2" t="inlineStr"/>
+      <c r="V181" s="2" t="inlineStr"/>
+      <c r="W181" s="2" t="inlineStr"/>
+      <c r="X181" s="2" t="inlineStr"/>
+      <c r="Y181" s="2" t="inlineStr"/>
+      <c r="Z181" s="2" t="inlineStr"/>
+      <c r="AA181" s="2" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>Pran Wines</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr"/>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>168428</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>Guangzhou</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr"/>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>No. 15 Xing'an Road, Tianhe District</t>
+        </is>
+      </c>
+      <c r="H182" s="2" t="inlineStr"/>
+      <c r="I182" s="2" t="inlineStr">
+        <is>
+          <t>http://www.pranwines.com</t>
+        </is>
+      </c>
+      <c r="J182" s="2" t="inlineStr"/>
+      <c r="K182" s="2" t="inlineStr"/>
+      <c r="L182" s="2" t="inlineStr"/>
+      <c r="M182" s="2" t="inlineStr"/>
+      <c r="N182" s="2" t="inlineStr">
+        <is>
+          <t>jassiedong@pranwines.com</t>
+        </is>
+      </c>
+      <c r="O182" s="2" t="inlineStr">
+        <is>
+          <t>+86 20 3861 9630</t>
+        </is>
+      </c>
+      <c r="P182" s="2" t="inlineStr"/>
+      <c r="Q182" s="2" t="inlineStr"/>
+      <c r="R182" s="2" t="inlineStr"/>
+      <c r="S182" s="2" t="inlineStr"/>
+      <c r="T182" s="2" t="inlineStr"/>
+      <c r="U182" s="2" t="inlineStr"/>
+      <c r="V182" s="2" t="inlineStr"/>
+      <c r="W182" s="2" t="inlineStr">
+        <is>
+          <t>Jassie Dong</t>
+        </is>
+      </c>
+      <c r="X182" s="2" t="inlineStr">
+        <is>
+          <t>Deputy General Manager</t>
+        </is>
+      </c>
+      <c r="Y182" s="2" t="inlineStr"/>
+      <c r="Z182" s="2" t="inlineStr"/>
+      <c r="AA182" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jassie-dong-a351b754/</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>Mingyin International</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr"/>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>168427</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
+        <is>
+          <t>Shanghai</t>
+        </is>
+      </c>
+      <c r="F183" s="2" t="inlineStr"/>
+      <c r="G183" s="2" t="inlineStr">
+        <is>
+          <t>No. 1000 Jinhai Road, West Wing, 4th Floor, Building 31</t>
+        </is>
+      </c>
+      <c r="H183" s="2" t="inlineStr"/>
+      <c r="I183" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mingyin.cc</t>
+        </is>
+      </c>
+      <c r="J183" s="2" t="inlineStr"/>
+      <c r="K183" s="2" t="inlineStr"/>
+      <c r="L183" s="2" t="inlineStr"/>
+      <c r="M183" s="2" t="inlineStr"/>
+      <c r="N183" s="2" t="inlineStr">
+        <is>
+          <t>info@MY5199.COM</t>
+        </is>
+      </c>
+      <c r="O183" s="2" t="inlineStr"/>
+      <c r="P183" s="2" t="inlineStr"/>
+      <c r="Q183" s="2" t="inlineStr"/>
+      <c r="R183" s="2" t="inlineStr"/>
+      <c r="S183" s="2" t="inlineStr"/>
+      <c r="T183" s="2" t="inlineStr"/>
+      <c r="U183" s="2" t="inlineStr"/>
+      <c r="V183" s="2" t="inlineStr"/>
+      <c r="W183" s="2" t="inlineStr"/>
+      <c r="X183" s="2" t="inlineStr"/>
+      <c r="Y183" s="2" t="inlineStr"/>
+      <c r="Z183" s="2" t="inlineStr"/>
+      <c r="AA183" s="2" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>Chengdu Baolang / Louis French Wine</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr"/>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>168426</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>Chengdu</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="inlineStr"/>
+      <c r="G184" s="2" t="inlineStr">
+        <is>
+          <t>No. 3399, Section 2, Muhua Road, Tianfu New Area</t>
+        </is>
+      </c>
+      <c r="H184" s="2" t="inlineStr"/>
+      <c r="I184" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fglyzy.com</t>
+        </is>
+      </c>
+      <c r="J184" s="2" t="inlineStr"/>
+      <c r="K184" s="2" t="inlineStr"/>
+      <c r="L184" s="2" t="inlineStr"/>
+      <c r="M184" s="2" t="inlineStr"/>
+      <c r="N184" s="2" t="inlineStr">
+        <is>
+          <t>fglyzy@126.com</t>
+        </is>
+      </c>
+      <c r="O184" s="2" t="inlineStr">
+        <is>
+          <t>+86 28 8266 6777</t>
+        </is>
+      </c>
+      <c r="P184" s="2" t="inlineStr"/>
+      <c r="Q184" s="2" t="inlineStr"/>
+      <c r="R184" s="2" t="inlineStr"/>
+      <c r="S184" s="2" t="inlineStr"/>
+      <c r="T184" s="2" t="inlineStr"/>
+      <c r="U184" s="2" t="inlineStr"/>
+      <c r="V184" s="2" t="inlineStr"/>
+      <c r="W184" s="2" t="inlineStr"/>
+      <c r="X184" s="2" t="inlineStr"/>
+      <c r="Y184" s="2" t="inlineStr"/>
+      <c r="Z184" s="2" t="inlineStr"/>
+      <c r="AA184" s="2" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>Anhui Hanrong Import &amp; Export</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr"/>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>168423</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="inlineStr">
+        <is>
+          <t>Hefei City</t>
+        </is>
+      </c>
+      <c r="F185" s="2" t="inlineStr">
+        <is>
+          <t>Anhui Province</t>
+        </is>
+      </c>
+      <c r="G185" s="2" t="inlineStr">
+        <is>
+          <t>2nd Floor, Electronics Building, Anhui University Science Park, High-tech Zone</t>
+        </is>
+      </c>
+      <c r="H185" s="2" t="inlineStr"/>
+      <c r="I185" s="2" t="inlineStr">
+        <is>
+          <t>http://51h9.com</t>
+        </is>
+      </c>
+      <c r="J185" s="2" t="inlineStr"/>
+      <c r="K185" s="2" t="inlineStr"/>
+      <c r="L185" s="2" t="inlineStr"/>
+      <c r="M185" s="2" t="inlineStr"/>
+      <c r="N185" s="2" t="inlineStr">
+        <is>
+          <t>1046913943@QQ.com</t>
+        </is>
+      </c>
+      <c r="O185" s="2" t="inlineStr">
+        <is>
+          <t>+86 551 6512 8477</t>
+        </is>
+      </c>
+      <c r="P185" s="2" t="inlineStr"/>
+      <c r="Q185" s="2" t="inlineStr"/>
+      <c r="R185" s="2" t="inlineStr"/>
+      <c r="S185" s="2" t="inlineStr"/>
+      <c r="T185" s="2" t="inlineStr"/>
+      <c r="U185" s="2" t="inlineStr"/>
+      <c r="V185" s="2" t="inlineStr"/>
+      <c r="W185" s="2" t="inlineStr"/>
+      <c r="X185" s="2" t="inlineStr"/>
+      <c r="Y185" s="2" t="inlineStr"/>
+      <c r="Z185" s="2" t="inlineStr"/>
+      <c r="AA185" s="2" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>Rioja Siglo Fuzhou</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr"/>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>168422</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="inlineStr">
+        <is>
+          <t>Fuzhou</t>
+        </is>
+      </c>
+      <c r="F186" s="2" t="inlineStr"/>
+      <c r="G186" s="2" t="inlineStr">
+        <is>
+          <t>Rooms 420-423, Building 9, Taihe City Center Plaza, East Second Ring Road</t>
+        </is>
+      </c>
+      <c r="H186" s="2" t="inlineStr"/>
+      <c r="I186" s="2" t="inlineStr">
+        <is>
+          <t>https://fzriojasiglo.com</t>
+        </is>
+      </c>
+      <c r="J186" s="2" t="inlineStr"/>
+      <c r="K186" s="2" t="inlineStr"/>
+      <c r="L186" s="2" t="inlineStr"/>
+      <c r="M186" s="2" t="inlineStr"/>
+      <c r="N186" s="2" t="inlineStr">
+        <is>
+          <t>fuzhours@126.com</t>
+        </is>
+      </c>
+      <c r="O186" s="2" t="inlineStr">
+        <is>
+          <t>+86 591 8731 3719</t>
+        </is>
+      </c>
+      <c r="P186" s="2" t="inlineStr"/>
+      <c r="Q186" s="2" t="inlineStr"/>
+      <c r="R186" s="2" t="inlineStr"/>
+      <c r="S186" s="2" t="inlineStr"/>
+      <c r="T186" s="2" t="inlineStr"/>
+      <c r="U186" s="2" t="inlineStr"/>
+      <c r="V186" s="2" t="inlineStr"/>
+      <c r="W186" s="2" t="inlineStr">
+        <is>
+          <t>Yu Lin Zheng</t>
+        </is>
+      </c>
+      <c r="X186" s="2" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="Y186" s="2" t="inlineStr"/>
+      <c r="Z186" s="2" t="inlineStr"/>
+      <c r="AA186" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/%E6%9E%97%E9%83%91-%E7%8E%89-yu-lin-zheng-821ba963/</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>Fanyu (Shanghai) International Trade Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr"/>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>168421</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="inlineStr">
+        <is>
+          <t>Xiamen City</t>
+        </is>
+      </c>
+      <c r="F187" s="2" t="inlineStr">
+        <is>
+          <t>Fujian Province</t>
+        </is>
+      </c>
+      <c r="G187" s="2" t="inlineStr">
+        <is>
+          <t>Room 101, No. 53, Haijing Middle Road</t>
+        </is>
+      </c>
+      <c r="H187" s="2" t="inlineStr"/>
+      <c r="I187" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fanyuguoji.com</t>
+        </is>
+      </c>
+      <c r="J187" s="2" t="inlineStr"/>
+      <c r="K187" s="2" t="inlineStr"/>
+      <c r="L187" s="2" t="inlineStr"/>
+      <c r="M187" s="2" t="inlineStr"/>
+      <c r="N187" s="2" t="inlineStr">
+        <is>
+          <t>447869361@qq.com</t>
+        </is>
+      </c>
+      <c r="O187" s="2" t="inlineStr">
+        <is>
+          <t>+86 592 555 2275</t>
+        </is>
+      </c>
+      <c r="P187" s="2" t="inlineStr"/>
+      <c r="Q187" s="2" t="inlineStr"/>
+      <c r="R187" s="2" t="inlineStr"/>
+      <c r="S187" s="2" t="inlineStr"/>
+      <c r="T187" s="2" t="inlineStr"/>
+      <c r="U187" s="2" t="inlineStr"/>
+      <c r="V187" s="2" t="inlineStr"/>
+      <c r="W187" s="2" t="inlineStr"/>
+      <c r="X187" s="2" t="inlineStr"/>
+      <c r="Y187" s="2" t="inlineStr"/>
+      <c r="Z187" s="2" t="inlineStr"/>
+      <c r="AA187" s="2" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>Tang Connection International Trading (Shanghai) Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr"/>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="inlineStr">
+        <is>
+          <t>Shanghai</t>
+        </is>
+      </c>
+      <c r="F188" s="2" t="inlineStr"/>
+      <c r="G188" s="2" t="inlineStr">
+        <is>
+          <t>Room 517, 5th Floor, Nash Space, No. 788 Jinshajiang Road</t>
+        </is>
+      </c>
+      <c r="H188" s="2" t="inlineStr"/>
+      <c r="I188" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tangconnection.com</t>
+        </is>
+      </c>
+      <c r="J188" s="2" t="inlineStr"/>
+      <c r="K188" s="2" t="inlineStr"/>
+      <c r="L188" s="2" t="inlineStr"/>
+      <c r="M188" s="2" t="inlineStr"/>
+      <c r="N188" s="2" t="inlineStr">
+        <is>
+          <t>hztymy@163.com</t>
+        </is>
+      </c>
+      <c r="O188" s="2" t="inlineStr">
+        <is>
+          <t>+86 21 5285 7308</t>
+        </is>
+      </c>
+      <c r="P188" s="2" t="inlineStr"/>
+      <c r="Q188" s="2" t="inlineStr"/>
+      <c r="R188" s="2" t="inlineStr"/>
+      <c r="S188" s="2" t="inlineStr"/>
+      <c r="T188" s="2" t="inlineStr"/>
+      <c r="U188" s="2" t="inlineStr"/>
+      <c r="V188" s="2" t="inlineStr"/>
+      <c r="W188" s="2" t="inlineStr"/>
+      <c r="X188" s="2" t="inlineStr"/>
+      <c r="Y188" s="2" t="inlineStr"/>
+      <c r="Z188" s="2" t="inlineStr"/>
+      <c r="AA188" s="2" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>Yinda Wine</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="inlineStr"/>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>168417</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="inlineStr">
+        <is>
+          <t>Kunming</t>
+        </is>
+      </c>
+      <c r="F189" s="2" t="inlineStr"/>
+      <c r="G189" s="2" t="inlineStr">
+        <is>
+          <t>5th Floor, Building N, Xinying Weilong Garden</t>
+        </is>
+      </c>
+      <c r="H189" s="2" t="inlineStr"/>
+      <c r="I189" s="2" t="inlineStr">
+        <is>
+          <t>https://ydmjk.com</t>
+        </is>
+      </c>
+      <c r="J189" s="2" t="inlineStr"/>
+      <c r="K189" s="2" t="inlineStr"/>
+      <c r="L189" s="2" t="inlineStr"/>
+      <c r="M189" s="2" t="inlineStr"/>
+      <c r="N189" s="2" t="inlineStr">
+        <is>
+          <t>ydmjk@vip.qq.com</t>
+        </is>
+      </c>
+      <c r="O189" s="2" t="inlineStr"/>
+      <c r="P189" s="2" t="inlineStr"/>
+      <c r="Q189" s="2" t="inlineStr"/>
+      <c r="R189" s="2" t="inlineStr"/>
+      <c r="S189" s="2" t="inlineStr"/>
+      <c r="T189" s="2" t="inlineStr"/>
+      <c r="U189" s="2" t="inlineStr"/>
+      <c r="V189" s="2" t="inlineStr"/>
+      <c r="W189" s="2" t="inlineStr"/>
+      <c r="X189" s="2" t="inlineStr"/>
+      <c r="Y189" s="2" t="inlineStr"/>
+      <c r="Z189" s="2" t="inlineStr"/>
+      <c r="AA189" s="2" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>Qingdao Aofei Wine Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr"/>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>168416</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="inlineStr">
+        <is>
+          <t>Qingdao</t>
+        </is>
+      </c>
+      <c r="F190" s="2" t="inlineStr"/>
+      <c r="G190" s="2" t="inlineStr">
+        <is>
+          <t>No. 5-3, Yan'erdao Road, Shinan District</t>
+        </is>
+      </c>
+      <c r="H190" s="2" t="inlineStr"/>
+      <c r="I190" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aofeike.cn</t>
+        </is>
+      </c>
+      <c r="J190" s="2" t="inlineStr"/>
+      <c r="K190" s="2" t="inlineStr"/>
+      <c r="L190" s="2" t="inlineStr"/>
+      <c r="M190" s="2" t="inlineStr"/>
+      <c r="N190" s="2" t="inlineStr">
+        <is>
+          <t>zzf@aofeike.cn</t>
+        </is>
+      </c>
+      <c r="O190" s="2" t="inlineStr">
+        <is>
+          <t>+86 532 8571 7791</t>
+        </is>
+      </c>
+      <c r="P190" s="2" t="inlineStr"/>
+      <c r="Q190" s="2" t="inlineStr"/>
+      <c r="R190" s="2" t="inlineStr"/>
+      <c r="S190" s="2" t="inlineStr"/>
+      <c r="T190" s="2" t="inlineStr"/>
+      <c r="U190" s="2" t="inlineStr"/>
+      <c r="V190" s="2" t="inlineStr"/>
+      <c r="W190" s="2" t="inlineStr"/>
+      <c r="X190" s="2" t="inlineStr"/>
+      <c r="Y190" s="2" t="inlineStr"/>
+      <c r="Z190" s="2" t="inlineStr"/>
+      <c r="AA190" s="2" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>Inalca Food &amp; Beverage China</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr"/>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>168415</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="inlineStr">
+        <is>
+          <t>Shanghai</t>
+        </is>
+      </c>
+      <c r="F191" s="2" t="inlineStr"/>
+      <c r="G191" s="2" t="inlineStr">
+        <is>
+          <t>4th Floor, Block B, Building 1, No. 158 Xuxiang Road</t>
+        </is>
+      </c>
+      <c r="H191" s="2" t="inlineStr"/>
+      <c r="I191" s="2" t="inlineStr">
+        <is>
+          <t>https://www.inalcafb.com.cn</t>
+        </is>
+      </c>
+      <c r="J191" s="2" t="inlineStr"/>
+      <c r="K191" s="2" t="inlineStr"/>
+      <c r="L191" s="2" t="inlineStr"/>
+      <c r="M191" s="2" t="inlineStr"/>
+      <c r="N191" s="2" t="inlineStr">
+        <is>
+          <t>info@inalcafb.com.cn</t>
+        </is>
+      </c>
+      <c r="O191" s="2" t="inlineStr"/>
+      <c r="P191" s="2" t="inlineStr"/>
+      <c r="Q191" s="2" t="inlineStr"/>
+      <c r="R191" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/if&amp;b-china/</t>
+        </is>
+      </c>
+      <c r="S191" s="2" t="inlineStr"/>
+      <c r="T191" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/inalcafb_china/</t>
+        </is>
+      </c>
+      <c r="U191" s="2" t="inlineStr"/>
+      <c r="V191" s="2" t="inlineStr"/>
+      <c r="W191" s="2" t="inlineStr">
+        <is>
+          <t>Davide Cavetti</t>
+        </is>
+      </c>
+      <c r="X191" s="2" t="inlineStr">
+        <is>
+          <t>Area Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y191" s="2" t="inlineStr"/>
+      <c r="Z191" s="2" t="inlineStr"/>
+      <c r="AA191" s="2" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/davide-cavetti-533241163</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>Inalca Food &amp; Beverage China</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr"/>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>168415</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="inlineStr">
+        <is>
+          <t>Shanghai</t>
+        </is>
+      </c>
+      <c r="F192" s="2" t="inlineStr"/>
+      <c r="G192" s="2" t="inlineStr">
+        <is>
+          <t>4th Floor, Block B, Building 1, No. 158 Xuxiang Road</t>
+        </is>
+      </c>
+      <c r="H192" s="2" t="inlineStr"/>
+      <c r="I192" s="2" t="inlineStr">
+        <is>
+          <t>https://www.inalcafb.com.cn</t>
+        </is>
+      </c>
+      <c r="J192" s="2" t="inlineStr"/>
+      <c r="K192" s="2" t="inlineStr"/>
+      <c r="L192" s="2" t="inlineStr"/>
+      <c r="M192" s="2" t="inlineStr"/>
+      <c r="N192" s="2" t="inlineStr">
+        <is>
+          <t>info@inalcafb.com.cn</t>
+        </is>
+      </c>
+      <c r="O192" s="2" t="inlineStr"/>
+      <c r="P192" s="2" t="inlineStr"/>
+      <c r="Q192" s="2" t="inlineStr"/>
+      <c r="R192" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/if&amp;b-china/</t>
+        </is>
+      </c>
+      <c r="S192" s="2" t="inlineStr"/>
+      <c r="T192" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/inalcafb_china/</t>
+        </is>
+      </c>
+      <c r="U192" s="2" t="inlineStr"/>
+      <c r="V192" s="2" t="inlineStr"/>
+      <c r="W192" s="2" t="inlineStr">
+        <is>
+          <t>Costanza Cascino</t>
+        </is>
+      </c>
+      <c r="X192" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y192" s="2" t="inlineStr"/>
+      <c r="Z192" s="2" t="inlineStr"/>
+      <c r="AA192" s="2" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/costanza-cascino-5854a287</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>Inalca Food &amp; Beverage China</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="inlineStr"/>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>168415</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E193" s="2" t="inlineStr">
+        <is>
+          <t>Shanghai</t>
+        </is>
+      </c>
+      <c r="F193" s="2" t="inlineStr"/>
+      <c r="G193" s="2" t="inlineStr">
+        <is>
+          <t>4th Floor, Block B, Building 1, No. 158 Xuxiang Road</t>
+        </is>
+      </c>
+      <c r="H193" s="2" t="inlineStr"/>
+      <c r="I193" s="2" t="inlineStr">
+        <is>
+          <t>https://www.inalcafb.com.cn</t>
+        </is>
+      </c>
+      <c r="J193" s="2" t="inlineStr"/>
+      <c r="K193" s="2" t="inlineStr"/>
+      <c r="L193" s="2" t="inlineStr"/>
+      <c r="M193" s="2" t="inlineStr"/>
+      <c r="N193" s="2" t="inlineStr">
+        <is>
+          <t>info@inalcafb.com.cn</t>
+        </is>
+      </c>
+      <c r="O193" s="2" t="inlineStr"/>
+      <c r="P193" s="2" t="inlineStr"/>
+      <c r="Q193" s="2" t="inlineStr"/>
+      <c r="R193" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/if&amp;b-china/</t>
+        </is>
+      </c>
+      <c r="S193" s="2" t="inlineStr"/>
+      <c r="T193" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/inalcafb_china/</t>
+        </is>
+      </c>
+      <c r="U193" s="2" t="inlineStr"/>
+      <c r="V193" s="2" t="inlineStr"/>
+      <c r="W193" s="2" t="inlineStr">
+        <is>
+          <t>Wenlan Ye</t>
+        </is>
+      </c>
+      <c r="X193" s="2" t="inlineStr">
+        <is>
+          <t>Supply Chain Manager</t>
+        </is>
+      </c>
+      <c r="Y193" s="2" t="inlineStr"/>
+      <c r="Z193" s="2" t="inlineStr"/>
+      <c r="AA193" s="2" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/wenlan-ye</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>Kunming Bonheur Trading Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="inlineStr"/>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>168414</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="inlineStr">
+        <is>
+          <t>Kunming</t>
+        </is>
+      </c>
+      <c r="F194" s="2" t="inlineStr"/>
+      <c r="G194" s="2" t="inlineStr">
+        <is>
+          <t>C21101, Jinse Junyuan, Panlong District</t>
+        </is>
+      </c>
+      <c r="H194" s="2" t="inlineStr"/>
+      <c r="I194" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lebonheur.cn</t>
+        </is>
+      </c>
+      <c r="J194" s="2" t="inlineStr"/>
+      <c r="K194" s="2" t="inlineStr"/>
+      <c r="L194" s="2" t="inlineStr"/>
+      <c r="M194" s="2" t="inlineStr"/>
+      <c r="N194" s="2" t="inlineStr">
+        <is>
+          <t>bonheur001@foxmail.com</t>
+        </is>
+      </c>
+      <c r="O194" s="2" t="inlineStr">
+        <is>
+          <t>+86 871 6701 1201</t>
+        </is>
+      </c>
+      <c r="P194" s="2" t="inlineStr"/>
+      <c r="Q194" s="2" t="inlineStr"/>
+      <c r="R194" s="2" t="inlineStr"/>
+      <c r="S194" s="2" t="inlineStr"/>
+      <c r="T194" s="2" t="inlineStr"/>
+      <c r="U194" s="2" t="inlineStr"/>
+      <c r="V194" s="2" t="inlineStr"/>
+      <c r="W194" s="2" t="inlineStr"/>
+      <c r="X194" s="2" t="inlineStr"/>
+      <c r="Y194" s="2" t="inlineStr"/>
+      <c r="Z194" s="2" t="inlineStr"/>
+      <c r="AA194" s="2" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>Guangzhou Longyi Trading Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="inlineStr"/>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>168413</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E195" s="2" t="inlineStr">
+        <is>
+          <t>Guangzhou</t>
+        </is>
+      </c>
+      <c r="F195" s="2" t="inlineStr"/>
+      <c r="G195" s="2" t="inlineStr">
+        <is>
+          <t>Room 1007, No. 140 Huangcun Road, Tianhe District</t>
+        </is>
+      </c>
+      <c r="H195" s="2" t="inlineStr"/>
+      <c r="I195" s="2" t="inlineStr">
+        <is>
+          <t>https://www.guangzhoulongyi.com</t>
+        </is>
+      </c>
+      <c r="J195" s="2" t="inlineStr"/>
+      <c r="K195" s="2" t="inlineStr"/>
+      <c r="L195" s="2" t="inlineStr"/>
+      <c r="M195" s="2" t="inlineStr"/>
+      <c r="N195" s="2" t="inlineStr">
+        <is>
+          <t>ww_wangzhe@vip.sina.com</t>
+        </is>
+      </c>
+      <c r="O195" s="2" t="inlineStr">
+        <is>
+          <t>+86 20 8756 8721</t>
+        </is>
+      </c>
+      <c r="P195" s="2" t="inlineStr"/>
+      <c r="Q195" s="2" t="inlineStr"/>
+      <c r="R195" s="2" t="inlineStr"/>
+      <c r="S195" s="2" t="inlineStr"/>
+      <c r="T195" s="2" t="inlineStr"/>
+      <c r="U195" s="2" t="inlineStr"/>
+      <c r="V195" s="2" t="inlineStr"/>
+      <c r="W195" s="2" t="inlineStr"/>
+      <c r="X195" s="2" t="inlineStr"/>
+      <c r="Y195" s="2" t="inlineStr"/>
+      <c r="Z195" s="2" t="inlineStr"/>
+      <c r="AA195" s="2" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>Zhejiang Jiujiajiu Technology Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="inlineStr"/>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>168412</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="inlineStr">
+        <is>
+          <t>Hangzhou</t>
+        </is>
+      </c>
+      <c r="F196" s="2" t="inlineStr">
+        <is>
+          <t>Zhejiang</t>
+        </is>
+      </c>
+      <c r="G196" s="2" t="inlineStr">
+        <is>
+          <t>No. 386 Beixiu Street, Banshan Subdistrict, Gongshu District</t>
+        </is>
+      </c>
+      <c r="H196" s="2" t="inlineStr"/>
+      <c r="I196" s="2" t="inlineStr">
+        <is>
+          <t>https://official.jiujiajiu.com</t>
+        </is>
+      </c>
+      <c r="J196" s="2" t="inlineStr"/>
+      <c r="K196" s="2" t="inlineStr"/>
+      <c r="L196" s="2" t="inlineStr"/>
+      <c r="M196" s="2" t="inlineStr"/>
+      <c r="N196" s="2" t="inlineStr">
+        <is>
+          <t>chengl@shangyuan.cn</t>
+        </is>
+      </c>
+      <c r="O196" s="2" t="inlineStr">
+        <is>
+          <t>+86 571 8682 6996</t>
+        </is>
+      </c>
+      <c r="P196" s="2" t="inlineStr"/>
+      <c r="Q196" s="2" t="inlineStr"/>
+      <c r="R196" s="2" t="inlineStr"/>
+      <c r="S196" s="2" t="inlineStr"/>
+      <c r="T196" s="2" t="inlineStr"/>
+      <c r="U196" s="2" t="inlineStr"/>
+      <c r="V196" s="2" t="inlineStr"/>
+      <c r="W196" s="2" t="inlineStr"/>
+      <c r="X196" s="2" t="inlineStr"/>
+      <c r="Y196" s="2" t="inlineStr"/>
+      <c r="Z196" s="2" t="inlineStr"/>
+      <c r="AA196" s="2" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>Hainan Zhonghuahang Group</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="inlineStr"/>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>168411</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="inlineStr">
+        <is>
+          <t>Haikou City</t>
+        </is>
+      </c>
+      <c r="F197" s="2" t="inlineStr">
+        <is>
+          <t>Hainan Province</t>
+        </is>
+      </c>
+      <c r="G197" s="2" t="inlineStr">
+        <is>
+          <t>No. 80, Haidian West Fifth Road, Meilan District</t>
+        </is>
+      </c>
+      <c r="H197" s="2" t="inlineStr"/>
+      <c r="I197" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hn-zhh.com</t>
+        </is>
+      </c>
+      <c r="J197" s="2" t="inlineStr"/>
+      <c r="K197" s="2" t="inlineStr"/>
+      <c r="L197" s="2" t="inlineStr"/>
+      <c r="M197" s="2" t="inlineStr"/>
+      <c r="N197" s="2" t="inlineStr">
+        <is>
+          <t>zhh-lxh@hn-zhh.com</t>
+        </is>
+      </c>
+      <c r="O197" s="2" t="inlineStr">
+        <is>
+          <t>+86 898 6625 8226</t>
+        </is>
+      </c>
+      <c r="P197" s="2" t="inlineStr"/>
+      <c r="Q197" s="2" t="inlineStr"/>
+      <c r="R197" s="2" t="inlineStr"/>
+      <c r="S197" s="2" t="inlineStr"/>
+      <c r="T197" s="2" t="inlineStr"/>
+      <c r="U197" s="2" t="inlineStr"/>
+      <c r="V197" s="2" t="inlineStr"/>
+      <c r="W197" s="2" t="inlineStr"/>
+      <c r="X197" s="2" t="inlineStr"/>
+      <c r="Y197" s="2" t="inlineStr"/>
+      <c r="Z197" s="2" t="inlineStr"/>
+      <c r="AA197" s="2" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>Gran Reserva Wines (Shenzhen) Trading Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr"/>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>168410</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="inlineStr">
+        <is>
+          <t>Shenzhen</t>
+        </is>
+      </c>
+      <c r="F198" s="2" t="inlineStr"/>
+      <c r="G198" s="2" t="inlineStr">
+        <is>
+          <t>Room 328, Block 6, Anhua Industrial Building, Chegongmiao, Futian</t>
+        </is>
+      </c>
+      <c r="H198" s="2" t="inlineStr"/>
+      <c r="I198" s="2" t="inlineStr">
+        <is>
+          <t>http://granreservawine.com</t>
+        </is>
+      </c>
+      <c r="J198" s="2" t="inlineStr"/>
+      <c r="K198" s="2" t="inlineStr"/>
+      <c r="L198" s="2" t="inlineStr"/>
+      <c r="M198" s="2" t="inlineStr"/>
+      <c r="N198" s="2" t="inlineStr">
+        <is>
+          <t>info@granreservawine.com</t>
+        </is>
+      </c>
+      <c r="O198" s="2" t="inlineStr">
+        <is>
+          <t>+86 755 8272 7616</t>
+        </is>
+      </c>
+      <c r="P198" s="2" t="inlineStr"/>
+      <c r="Q198" s="2" t="inlineStr"/>
+      <c r="R198" s="2" t="inlineStr"/>
+      <c r="S198" s="2" t="inlineStr"/>
+      <c r="T198" s="2" t="inlineStr"/>
+      <c r="U198" s="2" t="inlineStr"/>
+      <c r="V198" s="2" t="inlineStr"/>
+      <c r="W198" s="2" t="inlineStr"/>
+      <c r="X198" s="2" t="inlineStr"/>
+      <c r="Y198" s="2" t="inlineStr"/>
+      <c r="Z198" s="2" t="inlineStr"/>
+      <c r="AA198" s="2" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>Shanghai Wanmeixun Industrial Co., Ltd. / bevplus</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="inlineStr"/>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>168409</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="inlineStr">
+        <is>
+          <t>Shanghai</t>
+        </is>
+      </c>
+      <c r="F199" s="2" t="inlineStr"/>
+      <c r="G199" s="2" t="inlineStr">
+        <is>
+          <t>No. 126, Lane 68, Xiuyan West Road, Pudong New Area</t>
+        </is>
+      </c>
+      <c r="H199" s="2" t="inlineStr"/>
+      <c r="I199" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bevplus.co</t>
+        </is>
+      </c>
+      <c r="J199" s="2" t="inlineStr"/>
+      <c r="K199" s="2" t="inlineStr"/>
+      <c r="L199" s="2" t="inlineStr"/>
+      <c r="M199" s="2" t="inlineStr"/>
+      <c r="N199" s="2" t="inlineStr">
+        <is>
+          <t>info@bevplus.co</t>
+        </is>
+      </c>
+      <c r="O199" s="2" t="inlineStr">
+        <is>
+          <t>+86 21 6403 0934</t>
+        </is>
+      </c>
+      <c r="P199" s="2" t="inlineStr"/>
+      <c r="Q199" s="2" t="inlineStr"/>
+      <c r="R199" s="2" t="inlineStr"/>
+      <c r="S199" s="2" t="inlineStr"/>
+      <c r="T199" s="2" t="inlineStr"/>
+      <c r="U199" s="2" t="inlineStr"/>
+      <c r="V199" s="2" t="inlineStr"/>
+      <c r="W199" s="2" t="inlineStr"/>
+      <c r="X199" s="2" t="inlineStr"/>
+      <c r="Y199" s="2" t="inlineStr"/>
+      <c r="Z199" s="2" t="inlineStr"/>
+      <c r="AA199" s="2" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>Xiamen Oupinhui Import &amp; Export Co., Ltd. / Vindart</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="inlineStr"/>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>168408</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="inlineStr">
+        <is>
+          <t>Xiamen</t>
+        </is>
+      </c>
+      <c r="F200" s="2" t="inlineStr"/>
+      <c r="G200" s="2" t="inlineStr">
+        <is>
+          <t>Room 1001, Information Building, No. 27 Xinglong Road, Huli District</t>
+        </is>
+      </c>
+      <c r="H200" s="2" t="inlineStr"/>
+      <c r="I200" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vindart.cn</t>
+        </is>
+      </c>
+      <c r="J200" s="2" t="inlineStr"/>
+      <c r="K200" s="2" t="inlineStr"/>
+      <c r="L200" s="2" t="inlineStr"/>
+      <c r="M200" s="2" t="inlineStr"/>
+      <c r="N200" s="2" t="inlineStr">
+        <is>
+          <t>1545538372@qq.com</t>
+        </is>
+      </c>
+      <c r="O200" s="2" t="inlineStr">
+        <is>
+          <t>+86 592 578 9949</t>
+        </is>
+      </c>
+      <c r="P200" s="2" t="inlineStr"/>
+      <c r="Q200" s="2" t="inlineStr"/>
+      <c r="R200" s="2" t="inlineStr"/>
+      <c r="S200" s="2" t="inlineStr"/>
+      <c r="T200" s="2" t="inlineStr"/>
+      <c r="U200" s="2" t="inlineStr"/>
+      <c r="V200" s="2" t="inlineStr"/>
+      <c r="W200" s="2" t="inlineStr"/>
+      <c r="X200" s="2" t="inlineStr"/>
+      <c r="Y200" s="2" t="inlineStr"/>
+      <c r="Z200" s="2" t="inlineStr"/>
+      <c r="AA200" s="2" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>Qingdao Benfu International Trade Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="inlineStr"/>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>168406</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="inlineStr">
+        <is>
+          <t>Qingdao City</t>
+        </is>
+      </c>
+      <c r="F201" s="2" t="inlineStr">
+        <is>
+          <t>Shandong Province</t>
+        </is>
+      </c>
+      <c r="G201" s="2" t="inlineStr">
+        <is>
+          <t>618 Huishui Road</t>
+        </is>
+      </c>
+      <c r="H201" s="2" t="inlineStr"/>
+      <c r="I201" s="2" t="inlineStr">
+        <is>
+          <t>http://www.qdbenfu.com</t>
+        </is>
+      </c>
+      <c r="J201" s="2" t="inlineStr"/>
+      <c r="K201" s="2" t="inlineStr"/>
+      <c r="L201" s="2" t="inlineStr"/>
+      <c r="M201" s="2" t="inlineStr"/>
+      <c r="N201" s="2" t="inlineStr">
+        <is>
+          <t>david@qdbenfu.com</t>
+        </is>
+      </c>
+      <c r="O201" s="2" t="inlineStr">
+        <is>
+          <t>+86 532 8285 7979</t>
+        </is>
+      </c>
+      <c r="P201" s="2" t="inlineStr"/>
+      <c r="Q201" s="2" t="inlineStr"/>
+      <c r="R201" s="2" t="inlineStr"/>
+      <c r="S201" s="2" t="inlineStr"/>
+      <c r="T201" s="2" t="inlineStr"/>
+      <c r="U201" s="2" t="inlineStr"/>
+      <c r="V201" s="2" t="inlineStr"/>
+      <c r="W201" s="2" t="inlineStr"/>
+      <c r="X201" s="2" t="inlineStr"/>
+      <c r="Y201" s="2" t="inlineStr"/>
+      <c r="Z201" s="2" t="inlineStr"/>
+      <c r="AA201" s="2" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>Bluefite Wine Dongguan</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="inlineStr"/>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>168405</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E202" s="2" t="inlineStr">
+        <is>
+          <t>Dongguan City</t>
+        </is>
+      </c>
+      <c r="F202" s="2" t="inlineStr"/>
+      <c r="G202" s="2" t="inlineStr">
+        <is>
+          <t>Block A, Fortune Plaza, Nancheng District</t>
+        </is>
+      </c>
+      <c r="H202" s="2" t="inlineStr"/>
+      <c r="I202" s="2" t="inlineStr">
+        <is>
+          <t>https://bluefite.com</t>
+        </is>
+      </c>
+      <c r="J202" s="2" t="inlineStr"/>
+      <c r="K202" s="2" t="inlineStr"/>
+      <c r="L202" s="2" t="inlineStr"/>
+      <c r="M202" s="2" t="inlineStr"/>
+      <c r="N202" s="2" t="inlineStr">
+        <is>
+          <t>lanfei@bluefite.com</t>
+        </is>
+      </c>
+      <c r="O202" s="2" t="inlineStr">
+        <is>
+          <t>+86 769 8983 6899</t>
+        </is>
+      </c>
+      <c r="P202" s="2" t="inlineStr"/>
+      <c r="Q202" s="2" t="inlineStr"/>
+      <c r="R202" s="2" t="inlineStr"/>
+      <c r="S202" s="2" t="inlineStr"/>
+      <c r="T202" s="2" t="inlineStr"/>
+      <c r="U202" s="2" t="inlineStr"/>
+      <c r="V202" s="2" t="inlineStr"/>
+      <c r="W202" s="2" t="inlineStr"/>
+      <c r="X202" s="2" t="inlineStr"/>
+      <c r="Y202" s="2" t="inlineStr"/>
+      <c r="Z202" s="2" t="inlineStr"/>
+      <c r="AA202" s="2" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>Curve Wines</t>
+        </is>
+      </c>
+      <c r="B203" s="2" t="inlineStr"/>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>168404</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="inlineStr">
+        <is>
+          <t>Shanghai</t>
+        </is>
+      </c>
+      <c r="F203" s="2" t="inlineStr">
+        <is>
+          <t>Shanghai</t>
+        </is>
+      </c>
+      <c r="G203" s="2" t="inlineStr">
+        <is>
+          <t>580 West Nanjing Road</t>
+        </is>
+      </c>
+      <c r="H203" s="2" t="inlineStr"/>
+      <c r="I203" s="2" t="inlineStr">
+        <is>
+          <t>https://www.curvewine.com</t>
+        </is>
+      </c>
+      <c r="J203" s="2" t="inlineStr"/>
+      <c r="K203" s="2" t="inlineStr"/>
+      <c r="L203" s="2" t="inlineStr"/>
+      <c r="M203" s="2" t="inlineStr"/>
+      <c r="N203" s="2" t="inlineStr">
+        <is>
+          <t>info@curvewine.com</t>
+        </is>
+      </c>
+      <c r="O203" s="2" t="inlineStr"/>
+      <c r="P203" s="2" t="inlineStr"/>
+      <c r="Q203" s="2" t="inlineStr"/>
+      <c r="R203" s="2" t="inlineStr"/>
+      <c r="S203" s="2" t="inlineStr"/>
+      <c r="T203" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/curve.wine/</t>
+        </is>
+      </c>
+      <c r="U203" s="2" t="inlineStr"/>
+      <c r="V203" s="2" t="inlineStr"/>
+      <c r="W203" s="2" t="inlineStr"/>
+      <c r="X203" s="2" t="inlineStr"/>
+      <c r="Y203" s="2" t="inlineStr"/>
+      <c r="Z203" s="2" t="inlineStr"/>
+      <c r="AA203" s="2" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>Zhuhai Gaobo Wine</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="inlineStr"/>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>168403</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="inlineStr">
+        <is>
+          <t>Zhuhai City</t>
+        </is>
+      </c>
+      <c r="F204" s="2" t="inlineStr">
+        <is>
+          <t>Guangdong Province</t>
+        </is>
+      </c>
+      <c r="G204" s="2" t="inlineStr">
+        <is>
+          <t>Room 201, No. 106 Lian'an Road, Gongbei, Xiangzhou District</t>
+        </is>
+      </c>
+      <c r="H204" s="2" t="inlineStr"/>
+      <c r="I204" s="2" t="inlineStr">
+        <is>
+          <t>https://zhgaobo.cn</t>
+        </is>
+      </c>
+      <c r="J204" s="2" t="inlineStr"/>
+      <c r="K204" s="2" t="inlineStr"/>
+      <c r="L204" s="2" t="inlineStr"/>
+      <c r="M204" s="2" t="inlineStr"/>
+      <c r="N204" s="2" t="inlineStr">
+        <is>
+          <t>13570603456@139.com</t>
+        </is>
+      </c>
+      <c r="O204" s="2" t="inlineStr">
+        <is>
+          <t>+86 756 811 9985</t>
+        </is>
+      </c>
+      <c r="P204" s="2" t="inlineStr"/>
+      <c r="Q204" s="2" t="inlineStr"/>
+      <c r="R204" s="2" t="inlineStr"/>
+      <c r="S204" s="2" t="inlineStr"/>
+      <c r="T204" s="2" t="inlineStr"/>
+      <c r="U204" s="2" t="inlineStr"/>
+      <c r="V204" s="2" t="inlineStr"/>
+      <c r="W204" s="2" t="inlineStr"/>
+      <c r="X204" s="2" t="inlineStr"/>
+      <c r="Y204" s="2" t="inlineStr"/>
+      <c r="Z204" s="2" t="inlineStr"/>
+      <c r="AA204" s="2" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>Andes Wines China</t>
+        </is>
+      </c>
+      <c r="B205" s="2" t="inlineStr"/>
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t>168402</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E205" s="2" t="inlineStr">
+        <is>
+          <t>Shenzhen</t>
+        </is>
+      </c>
+      <c r="F205" s="2" t="inlineStr">
+        <is>
+          <t>Guangdong</t>
+        </is>
+      </c>
+      <c r="G205" s="2" t="inlineStr">
+        <is>
+          <t>Tairan 6th Road, Tianan Community, Shatou Street, Futian District</t>
+        </is>
+      </c>
+      <c r="H205" s="2" t="inlineStr"/>
+      <c r="I205" s="2" t="inlineStr">
+        <is>
+          <t>https://andes-wines.com</t>
+        </is>
+      </c>
+      <c r="J205" s="2" t="inlineStr"/>
+      <c r="K205" s="2" t="inlineStr"/>
+      <c r="L205" s="2" t="inlineStr"/>
+      <c r="M205" s="2" t="inlineStr"/>
+      <c r="N205" s="2" t="inlineStr">
+        <is>
+          <t>andesLSP@163.com</t>
+        </is>
+      </c>
+      <c r="O205" s="2" t="inlineStr">
+        <is>
+          <t>+86 755 8384 9958</t>
+        </is>
+      </c>
+      <c r="P205" s="2" t="inlineStr"/>
+      <c r="Q205" s="2" t="inlineStr"/>
+      <c r="R205" s="2" t="inlineStr"/>
+      <c r="S205" s="2" t="inlineStr"/>
+      <c r="T205" s="2" t="inlineStr"/>
+      <c r="U205" s="2" t="inlineStr"/>
+      <c r="V205" s="2" t="inlineStr"/>
+      <c r="W205" s="2" t="inlineStr"/>
+      <c r="X205" s="2" t="inlineStr"/>
+      <c r="Y205" s="2" t="inlineStr"/>
+      <c r="Z205" s="2" t="inlineStr"/>
+      <c r="AA205" s="2" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>Cofco Corporation</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>Cofco Corporation</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>35571</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="inlineStr">
+        <is>
+          <t>Dongcheng</t>
+        </is>
+      </c>
+      <c r="F206" s="2" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="G206" s="2" t="inlineStr">
+        <is>
+          <t>Cofco Fortune Plaza, No.8, Chao Yang Men South St., Chao Yang District</t>
+        </is>
+      </c>
+      <c r="H206" s="2" t="inlineStr">
+        <is>
+          <t>100020</t>
+        </is>
+      </c>
+      <c r="I206" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cofco.com, https://www.cofcointernational.com</t>
+        </is>
+      </c>
+      <c r="J206" s="2" t="inlineStr"/>
+      <c r="K206" s="2" t="inlineStr"/>
+      <c r="L206" s="2" t="inlineStr">
+        <is>
+          <t>1806</t>
+        </is>
+      </c>
+      <c r="M206" s="2" t="inlineStr"/>
+      <c r="N206" s="2" t="inlineStr">
+        <is>
+          <t>cofco-news@cofco.com</t>
+        </is>
+      </c>
+      <c r="O206" s="2" t="inlineStr">
+        <is>
+          <t>+86 10 8500 6688</t>
+        </is>
+      </c>
+      <c r="P206" s="2" t="inlineStr">
+        <is>
+          <t>1983</t>
+        </is>
+      </c>
+      <c r="Q206" s="2" t="inlineStr">
+        <is>
+          <t>91110000101100414N</t>
+        </is>
+      </c>
+      <c r="R206" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/cofco-corporation</t>
+        </is>
+      </c>
+      <c r="S206" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/COFCO1949/</t>
+        </is>
+      </c>
+      <c r="T206" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cofcointl/</t>
+        </is>
+      </c>
+      <c r="U206" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/COFCOINTL</t>
+        </is>
+      </c>
+      <c r="V206" s="2" t="inlineStr"/>
+      <c r="W206" s="2" t="inlineStr">
+        <is>
+          <t>Jack Yang</t>
+        </is>
+      </c>
+      <c r="X206" s="2" t="inlineStr">
+        <is>
+          <t>Import And Brand Manager</t>
+        </is>
+      </c>
+      <c r="Y206" s="2" t="inlineStr"/>
+      <c r="Z206" s="2" t="inlineStr"/>
+      <c r="AA206" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jack-yang-86178a53/</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>Cofco Corporation</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>Cofco Corporation</t>
+        </is>
+      </c>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>35571</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="inlineStr">
+        <is>
+          <t>Dongcheng</t>
+        </is>
+      </c>
+      <c r="F207" s="2" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="G207" s="2" t="inlineStr">
+        <is>
+          <t>Cofco Fortune Plaza, No.8, Chao Yang Men South St., Chao Yang District</t>
+        </is>
+      </c>
+      <c r="H207" s="2" t="inlineStr">
+        <is>
+          <t>100020</t>
+        </is>
+      </c>
+      <c r="I207" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cofco.com, https://www.cofcointernational.com</t>
+        </is>
+      </c>
+      <c r="J207" s="2" t="inlineStr"/>
+      <c r="K207" s="2" t="inlineStr"/>
+      <c r="L207" s="2" t="inlineStr">
+        <is>
+          <t>1806</t>
+        </is>
+      </c>
+      <c r="M207" s="2" t="inlineStr"/>
+      <c r="N207" s="2" t="inlineStr">
+        <is>
+          <t>cofco-news@cofco.com</t>
+        </is>
+      </c>
+      <c r="O207" s="2" t="inlineStr">
+        <is>
+          <t>+86 10 8500 6688</t>
+        </is>
+      </c>
+      <c r="P207" s="2" t="inlineStr">
+        <is>
+          <t>1983</t>
+        </is>
+      </c>
+      <c r="Q207" s="2" t="inlineStr">
+        <is>
+          <t>91110000101100414N</t>
+        </is>
+      </c>
+      <c r="R207" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/cofco-corporation</t>
+        </is>
+      </c>
+      <c r="S207" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/COFCO1949/</t>
+        </is>
+      </c>
+      <c r="T207" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cofcointl/</t>
+        </is>
+      </c>
+      <c r="U207" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/COFCOINTL</t>
+        </is>
+      </c>
+      <c r="V207" s="2" t="inlineStr"/>
+      <c r="W207" s="2" t="inlineStr">
+        <is>
+          <t>Randy Zhou</t>
+        </is>
+      </c>
+      <c r="X207" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manger of Import Wine Division</t>
+        </is>
+      </c>
+      <c r="Y207" s="2" t="inlineStr"/>
+      <c r="Z207" s="2" t="inlineStr"/>
+      <c r="AA207" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/randy-zhou-04b80435/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_China.xlsx
+++ b/BWI/bestwine_output/bestwine_China.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA207"/>
+  <dimension ref="A1:AA214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -20294,6 +20294,585 @@
         </is>
       </c>
     </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>Guangzhou Enote Trading Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="inlineStr"/>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>168436</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E208" s="2" t="inlineStr">
+        <is>
+          <t>Guangzhou</t>
+        </is>
+      </c>
+      <c r="F208" s="2" t="inlineStr"/>
+      <c r="G208" s="2" t="inlineStr">
+        <is>
+          <t>Building F2, Xinsheng Industrial Park, No. 9 Henggangtou, Xintang Street, Tianhe District</t>
+        </is>
+      </c>
+      <c r="H208" s="2" t="inlineStr"/>
+      <c r="I208" s="2" t="inlineStr">
+        <is>
+          <t>http://www.enotewine.com</t>
+        </is>
+      </c>
+      <c r="J208" s="2" t="inlineStr"/>
+      <c r="K208" s="2" t="inlineStr"/>
+      <c r="L208" s="2" t="inlineStr"/>
+      <c r="M208" s="2" t="inlineStr"/>
+      <c r="N208" s="2" t="inlineStr">
+        <is>
+          <t>enote-ben@qq.com</t>
+        </is>
+      </c>
+      <c r="O208" s="2" t="inlineStr">
+        <is>
+          <t>+86 20 8525 1230</t>
+        </is>
+      </c>
+      <c r="P208" s="2" t="inlineStr"/>
+      <c r="Q208" s="2" t="inlineStr"/>
+      <c r="R208" s="2" t="inlineStr"/>
+      <c r="S208" s="2" t="inlineStr"/>
+      <c r="T208" s="2" t="inlineStr"/>
+      <c r="U208" s="2" t="inlineStr"/>
+      <c r="V208" s="2" t="inlineStr"/>
+      <c r="W208" s="2" t="inlineStr"/>
+      <c r="X208" s="2" t="inlineStr"/>
+      <c r="Y208" s="2" t="inlineStr"/>
+      <c r="Z208" s="2" t="inlineStr"/>
+      <c r="AA208" s="2" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>Chuangyi Import &amp; Export Trade</t>
+        </is>
+      </c>
+      <c r="B209" s="2" t="inlineStr"/>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>168435</t>
+        </is>
+      </c>
+      <c r="D209" s="2" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E209" s="2" t="inlineStr">
+        <is>
+          <t>Chengdu</t>
+        </is>
+      </c>
+      <c r="F209" s="2" t="inlineStr">
+        <is>
+          <t>Sichuan</t>
+        </is>
+      </c>
+      <c r="G209" s="2" t="inlineStr">
+        <is>
+          <t>705 7th floor, building 7, No 765, Tianfu Avenue</t>
+        </is>
+      </c>
+      <c r="H209" s="2" t="inlineStr"/>
+      <c r="I209" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kuaixiaohome.com</t>
+        </is>
+      </c>
+      <c r="J209" s="2" t="inlineStr"/>
+      <c r="K209" s="2" t="inlineStr"/>
+      <c r="L209" s="2" t="inlineStr"/>
+      <c r="M209" s="2" t="inlineStr"/>
+      <c r="N209" s="2" t="inlineStr">
+        <is>
+          <t>zhenghua@kuaixiaohome.com</t>
+        </is>
+      </c>
+      <c r="O209" s="2" t="inlineStr"/>
+      <c r="P209" s="2" t="inlineStr"/>
+      <c r="Q209" s="2" t="inlineStr"/>
+      <c r="R209" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/sichuan-chuangyi-science-and-technology-co-ltd/</t>
+        </is>
+      </c>
+      <c r="S209" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=61576626742194</t>
+        </is>
+      </c>
+      <c r="T209" s="2" t="inlineStr"/>
+      <c r="U209" s="2" t="inlineStr"/>
+      <c r="V209" s="2" t="inlineStr"/>
+      <c r="W209" s="2" t="inlineStr">
+        <is>
+          <t>YUNA YUAN</t>
+        </is>
+      </c>
+      <c r="X209" s="2" t="inlineStr">
+        <is>
+          <t>International Trade Specialist</t>
+        </is>
+      </c>
+      <c r="Y209" s="2" t="inlineStr"/>
+      <c r="Z209" s="2" t="inlineStr"/>
+      <c r="AA209" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/yuna-beverage-trade/</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>Chuangyi Import &amp; Export Trade</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="inlineStr"/>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>168435</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E210" s="2" t="inlineStr">
+        <is>
+          <t>Chengdu</t>
+        </is>
+      </c>
+      <c r="F210" s="2" t="inlineStr">
+        <is>
+          <t>Sichuan</t>
+        </is>
+      </c>
+      <c r="G210" s="2" t="inlineStr">
+        <is>
+          <t>705 7th floor, building 7, No 765, Tianfu Avenue</t>
+        </is>
+      </c>
+      <c r="H210" s="2" t="inlineStr"/>
+      <c r="I210" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kuaixiaohome.com</t>
+        </is>
+      </c>
+      <c r="J210" s="2" t="inlineStr"/>
+      <c r="K210" s="2" t="inlineStr"/>
+      <c r="L210" s="2" t="inlineStr"/>
+      <c r="M210" s="2" t="inlineStr"/>
+      <c r="N210" s="2" t="inlineStr">
+        <is>
+          <t>zhenghua@kuaixiaohome.com</t>
+        </is>
+      </c>
+      <c r="O210" s="2" t="inlineStr"/>
+      <c r="P210" s="2" t="inlineStr"/>
+      <c r="Q210" s="2" t="inlineStr"/>
+      <c r="R210" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/sichuan-chuangyi-science-and-technology-co-ltd/</t>
+        </is>
+      </c>
+      <c r="S210" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=61576626742194</t>
+        </is>
+      </c>
+      <c r="T210" s="2" t="inlineStr"/>
+      <c r="U210" s="2" t="inlineStr"/>
+      <c r="V210" s="2" t="inlineStr"/>
+      <c r="W210" s="2" t="inlineStr">
+        <is>
+          <t>Jaime (Hua) Zheng</t>
+        </is>
+      </c>
+      <c r="X210" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Import / Export Manager</t>
+        </is>
+      </c>
+      <c r="Y210" s="2" t="inlineStr"/>
+      <c r="Z210" s="2" t="inlineStr"/>
+      <c r="AA210" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jaime-zheng-62448691/</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>Arion Spirit &amp; Wine China</t>
+        </is>
+      </c>
+      <c r="B211" s="2" t="inlineStr"/>
+      <c r="C211" s="2" t="inlineStr">
+        <is>
+          <t>168433</t>
+        </is>
+      </c>
+      <c r="D211" s="2" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E211" s="2" t="inlineStr">
+        <is>
+          <t>Shanghai</t>
+        </is>
+      </c>
+      <c r="F211" s="2" t="inlineStr">
+        <is>
+          <t>Shanghai</t>
+        </is>
+      </c>
+      <c r="G211" s="2" t="inlineStr">
+        <is>
+          <t>15 Dongping Road, Room 408</t>
+        </is>
+      </c>
+      <c r="H211" s="2" t="inlineStr"/>
+      <c r="I211" s="2" t="inlineStr">
+        <is>
+          <t>https://arionchina.com</t>
+        </is>
+      </c>
+      <c r="J211" s="2" t="inlineStr"/>
+      <c r="K211" s="2" t="inlineStr"/>
+      <c r="L211" s="2" t="inlineStr"/>
+      <c r="M211" s="2" t="inlineStr"/>
+      <c r="N211" s="2" t="inlineStr">
+        <is>
+          <t>INFO@ARIONINTL.COM</t>
+        </is>
+      </c>
+      <c r="O211" s="2" t="inlineStr"/>
+      <c r="P211" s="2" t="inlineStr"/>
+      <c r="Q211" s="2" t="inlineStr"/>
+      <c r="R211" s="2" t="inlineStr"/>
+      <c r="S211" s="2" t="inlineStr"/>
+      <c r="T211" s="2" t="inlineStr"/>
+      <c r="U211" s="2" t="inlineStr"/>
+      <c r="V211" s="2" t="inlineStr"/>
+      <c r="W211" s="2" t="inlineStr"/>
+      <c r="X211" s="2" t="inlineStr"/>
+      <c r="Y211" s="2" t="inlineStr"/>
+      <c r="Z211" s="2" t="inlineStr"/>
+      <c r="AA211" s="2" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>Wenrong International Business Trading (Shanghai) Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="B212" s="2" t="inlineStr"/>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>168432</t>
+        </is>
+      </c>
+      <c r="D212" s="2" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E212" s="2" t="inlineStr">
+        <is>
+          <t>Shanghai</t>
+        </is>
+      </c>
+      <c r="F212" s="2" t="inlineStr">
+        <is>
+          <t>Shanghai</t>
+        </is>
+      </c>
+      <c r="G212" s="2" t="inlineStr">
+        <is>
+          <t>FA4075, 2 bldg, #598 Guanghua Road</t>
+        </is>
+      </c>
+      <c r="H212" s="2" t="inlineStr">
+        <is>
+          <t>200023</t>
+        </is>
+      </c>
+      <c r="I212" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wengrong-trade.com</t>
+        </is>
+      </c>
+      <c r="J212" s="2" t="inlineStr"/>
+      <c r="K212" s="2" t="inlineStr"/>
+      <c r="L212" s="2" t="inlineStr"/>
+      <c r="M212" s="2" t="inlineStr"/>
+      <c r="N212" s="2" t="inlineStr">
+        <is>
+          <t>sales@wengrong-trade.com</t>
+        </is>
+      </c>
+      <c r="O212" s="2" t="inlineStr">
+        <is>
+          <t>+86 21 5020 6776</t>
+        </is>
+      </c>
+      <c r="P212" s="2" t="inlineStr"/>
+      <c r="Q212" s="2" t="inlineStr"/>
+      <c r="R212" s="2" t="inlineStr"/>
+      <c r="S212" s="2" t="inlineStr"/>
+      <c r="T212" s="2" t="inlineStr"/>
+      <c r="U212" s="2" t="inlineStr"/>
+      <c r="V212" s="2" t="inlineStr"/>
+      <c r="W212" s="2" t="inlineStr"/>
+      <c r="X212" s="2" t="inlineStr"/>
+      <c r="Y212" s="2" t="inlineStr"/>
+      <c r="Z212" s="2" t="inlineStr"/>
+      <c r="AA212" s="2" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t>Cofco Corporation</t>
+        </is>
+      </c>
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>Cofco Corporation</t>
+        </is>
+      </c>
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t>35571</t>
+        </is>
+      </c>
+      <c r="D213" s="2" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E213" s="2" t="inlineStr">
+        <is>
+          <t>Dongcheng</t>
+        </is>
+      </c>
+      <c r="F213" s="2" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="G213" s="2" t="inlineStr">
+        <is>
+          <t>Cofco Fortune Plaza, No.8, Chao Yang Men South St., Chao Yang District</t>
+        </is>
+      </c>
+      <c r="H213" s="2" t="inlineStr">
+        <is>
+          <t>100020</t>
+        </is>
+      </c>
+      <c r="I213" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cofco.com, https://www.cofcointernational.com</t>
+        </is>
+      </c>
+      <c r="J213" s="2" t="inlineStr"/>
+      <c r="K213" s="2" t="inlineStr"/>
+      <c r="L213" s="2" t="inlineStr">
+        <is>
+          <t>1806</t>
+        </is>
+      </c>
+      <c r="M213" s="2" t="inlineStr"/>
+      <c r="N213" s="2" t="inlineStr">
+        <is>
+          <t>cofco-news@cofco.com</t>
+        </is>
+      </c>
+      <c r="O213" s="2" t="inlineStr">
+        <is>
+          <t>+86 10 8500 6688</t>
+        </is>
+      </c>
+      <c r="P213" s="2" t="inlineStr">
+        <is>
+          <t>1983</t>
+        </is>
+      </c>
+      <c r="Q213" s="2" t="inlineStr">
+        <is>
+          <t>91110000101100414N</t>
+        </is>
+      </c>
+      <c r="R213" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/cofco-corporation</t>
+        </is>
+      </c>
+      <c r="S213" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/COFCO1949/</t>
+        </is>
+      </c>
+      <c r="T213" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cofcointl/</t>
+        </is>
+      </c>
+      <c r="U213" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/COFCOINTL</t>
+        </is>
+      </c>
+      <c r="V213" s="2" t="inlineStr"/>
+      <c r="W213" s="2" t="inlineStr">
+        <is>
+          <t>Jack Yang</t>
+        </is>
+      </c>
+      <c r="X213" s="2" t="inlineStr">
+        <is>
+          <t>Import And Brand Manager</t>
+        </is>
+      </c>
+      <c r="Y213" s="2" t="inlineStr"/>
+      <c r="Z213" s="2" t="inlineStr"/>
+      <c r="AA213" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jack-yang-86178a53/</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>Cofco Corporation</t>
+        </is>
+      </c>
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>Cofco Corporation</t>
+        </is>
+      </c>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>35571</t>
+        </is>
+      </c>
+      <c r="D214" s="2" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E214" s="2" t="inlineStr">
+        <is>
+          <t>Dongcheng</t>
+        </is>
+      </c>
+      <c r="F214" s="2" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="G214" s="2" t="inlineStr">
+        <is>
+          <t>Cofco Fortune Plaza, No.8, Chao Yang Men South St., Chao Yang District</t>
+        </is>
+      </c>
+      <c r="H214" s="2" t="inlineStr">
+        <is>
+          <t>100020</t>
+        </is>
+      </c>
+      <c r="I214" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cofco.com, https://www.cofcointernational.com</t>
+        </is>
+      </c>
+      <c r="J214" s="2" t="inlineStr"/>
+      <c r="K214" s="2" t="inlineStr"/>
+      <c r="L214" s="2" t="inlineStr">
+        <is>
+          <t>1806</t>
+        </is>
+      </c>
+      <c r="M214" s="2" t="inlineStr"/>
+      <c r="N214" s="2" t="inlineStr">
+        <is>
+          <t>cofco-news@cofco.com</t>
+        </is>
+      </c>
+      <c r="O214" s="2" t="inlineStr">
+        <is>
+          <t>+86 10 8500 6688</t>
+        </is>
+      </c>
+      <c r="P214" s="2" t="inlineStr">
+        <is>
+          <t>1983</t>
+        </is>
+      </c>
+      <c r="Q214" s="2" t="inlineStr">
+        <is>
+          <t>91110000101100414N</t>
+        </is>
+      </c>
+      <c r="R214" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/cofco-corporation</t>
+        </is>
+      </c>
+      <c r="S214" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/COFCO1949/</t>
+        </is>
+      </c>
+      <c r="T214" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cofcointl/</t>
+        </is>
+      </c>
+      <c r="U214" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/COFCOINTL</t>
+        </is>
+      </c>
+      <c r="V214" s="2" t="inlineStr"/>
+      <c r="W214" s="2" t="inlineStr">
+        <is>
+          <t>Randy Zhou</t>
+        </is>
+      </c>
+      <c r="X214" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manger of Import Wine Division</t>
+        </is>
+      </c>
+      <c r="Y214" s="2" t="inlineStr"/>
+      <c r="Z214" s="2" t="inlineStr"/>
+      <c r="AA214" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/randy-zhou-04b80435/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_China.xlsx
+++ b/BWI/bestwine_output/bestwine_China.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA214"/>
+  <dimension ref="A1:AA216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -20873,6 +20873,232 @@
         </is>
       </c>
     </row>
+    <row r="215">
+      <c r="A215" s="2" t="inlineStr">
+        <is>
+          <t>Cofco Corporation</t>
+        </is>
+      </c>
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t>Cofco Corporation</t>
+        </is>
+      </c>
+      <c r="C215" s="2" t="inlineStr">
+        <is>
+          <t>35571</t>
+        </is>
+      </c>
+      <c r="D215" s="2" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E215" s="2" t="inlineStr">
+        <is>
+          <t>Dongcheng</t>
+        </is>
+      </c>
+      <c r="F215" s="2" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="G215" s="2" t="inlineStr">
+        <is>
+          <t>Cofco Fortune Plaza, No.8, Chao Yang Men South St., Chao Yang District</t>
+        </is>
+      </c>
+      <c r="H215" s="2" t="inlineStr">
+        <is>
+          <t>100020</t>
+        </is>
+      </c>
+      <c r="I215" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cofco.com, https://www.cofcointernational.com</t>
+        </is>
+      </c>
+      <c r="J215" s="2" t="inlineStr"/>
+      <c r="K215" s="2" t="inlineStr"/>
+      <c r="L215" s="2" t="inlineStr">
+        <is>
+          <t>1806</t>
+        </is>
+      </c>
+      <c r="M215" s="2" t="inlineStr"/>
+      <c r="N215" s="2" t="inlineStr">
+        <is>
+          <t>cofco-news@cofco.com</t>
+        </is>
+      </c>
+      <c r="O215" s="2" t="inlineStr">
+        <is>
+          <t>+86 10 8500 6688</t>
+        </is>
+      </c>
+      <c r="P215" s="2" t="inlineStr">
+        <is>
+          <t>1983</t>
+        </is>
+      </c>
+      <c r="Q215" s="2" t="inlineStr">
+        <is>
+          <t>91110000101100414N</t>
+        </is>
+      </c>
+      <c r="R215" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/cofco-corporation</t>
+        </is>
+      </c>
+      <c r="S215" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/COFCO1949/</t>
+        </is>
+      </c>
+      <c r="T215" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cofcointl/</t>
+        </is>
+      </c>
+      <c r="U215" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/COFCOINTL</t>
+        </is>
+      </c>
+      <c r="V215" s="2" t="inlineStr"/>
+      <c r="W215" s="2" t="inlineStr">
+        <is>
+          <t>Jack Yang</t>
+        </is>
+      </c>
+      <c r="X215" s="2" t="inlineStr">
+        <is>
+          <t>Import And Brand Manager</t>
+        </is>
+      </c>
+      <c r="Y215" s="2" t="inlineStr"/>
+      <c r="Z215" s="2" t="inlineStr"/>
+      <c r="AA215" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jack-yang-86178a53/</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>Cofco Corporation</t>
+        </is>
+      </c>
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>Cofco Corporation</t>
+        </is>
+      </c>
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t>35571</t>
+        </is>
+      </c>
+      <c r="D216" s="2" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E216" s="2" t="inlineStr">
+        <is>
+          <t>Dongcheng</t>
+        </is>
+      </c>
+      <c r="F216" s="2" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="G216" s="2" t="inlineStr">
+        <is>
+          <t>Cofco Fortune Plaza, No.8, Chao Yang Men South St., Chao Yang District</t>
+        </is>
+      </c>
+      <c r="H216" s="2" t="inlineStr">
+        <is>
+          <t>100020</t>
+        </is>
+      </c>
+      <c r="I216" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cofco.com, https://www.cofcointernational.com</t>
+        </is>
+      </c>
+      <c r="J216" s="2" t="inlineStr"/>
+      <c r="K216" s="2" t="inlineStr"/>
+      <c r="L216" s="2" t="inlineStr">
+        <is>
+          <t>1806</t>
+        </is>
+      </c>
+      <c r="M216" s="2" t="inlineStr"/>
+      <c r="N216" s="2" t="inlineStr">
+        <is>
+          <t>cofco-news@cofco.com</t>
+        </is>
+      </c>
+      <c r="O216" s="2" t="inlineStr">
+        <is>
+          <t>+86 10 8500 6688</t>
+        </is>
+      </c>
+      <c r="P216" s="2" t="inlineStr">
+        <is>
+          <t>1983</t>
+        </is>
+      </c>
+      <c r="Q216" s="2" t="inlineStr">
+        <is>
+          <t>91110000101100414N</t>
+        </is>
+      </c>
+      <c r="R216" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/cofco-corporation</t>
+        </is>
+      </c>
+      <c r="S216" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/COFCO1949/</t>
+        </is>
+      </c>
+      <c r="T216" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cofcointl/</t>
+        </is>
+      </c>
+      <c r="U216" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/COFCOINTL</t>
+        </is>
+      </c>
+      <c r="V216" s="2" t="inlineStr"/>
+      <c r="W216" s="2" t="inlineStr">
+        <is>
+          <t>Randy Zhou</t>
+        </is>
+      </c>
+      <c r="X216" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manger of Import Wine Division</t>
+        </is>
+      </c>
+      <c r="Y216" s="2" t="inlineStr"/>
+      <c r="Z216" s="2" t="inlineStr"/>
+      <c r="AA216" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/randy-zhou-04b80435/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
